--- a/output/pdf_financials_xlsx/TIDE.P.xlsx
+++ b/output/pdf_financials_xlsx/TIDE.P.xlsx
@@ -2583,16 +2583,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.050957</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.050957</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.050957</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.050957</v>
       </c>
     </row>
     <row r="93">
@@ -3894,7 +3894,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TIDE.P.xlsx
+++ b/output/pdf_financials_xlsx/TIDE.P.xlsx
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.169979</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.277211</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.244455</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.218582</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.199115</v>
       </c>
     </row>
     <row r="35">
@@ -1288,19 +1288,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.169979</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.277211</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.244455</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.218582</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.199115</v>
       </c>
     </row>
     <row r="37">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
